--- a/config/excel/chapters.xlsx
+++ b/config/excel/chapters.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,47 +464,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>入门章节</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>第二章</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Boss 与高强度混合战</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>第三章</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>新怪种逐步登场，终局对战千足虫</t>
+          <t>30 关单章</t>
         </is>
       </c>
     </row>
